--- a/src/main/resources/template/持仓列表.xlsx
+++ b/src/main/resources/template/持仓列表.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gking\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\risk\src\main\resources\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67452B7C-2077-4089-96F9-470428FCF13B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C8B020F-00DA-45BE-949E-481ED90991CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,17 +25,21 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>合约</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>类型</t>
+    <t>代码</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>代码</t>
+    <t>日期</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>收盘价</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -73,12 +77,27 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -87,7 +106,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -368,18 +387,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:D1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/template/持仓列表.xlsx
+++ b/src/main/resources/template/持仓列表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\risk\src\main\resources\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C8B020F-00DA-45BE-949E-481ED90991CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2150DC8F-805F-4FF6-A278-29BA09DF762D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>合约</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -35,11 +35,15 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>日期</t>
+    <t>来源</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>收盘价</t>
+    <t>收盘价格</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>日期(yyy-MM-dd)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -47,7 +51,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -57,6 +61,15 @@
     </font>
     <font>
       <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
       <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
@@ -106,7 +119,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -387,25 +400,35 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="10.625" customWidth="1"/>
+    <col min="2" max="2" width="22.75" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.125" customWidth="1"/>
+    <col min="5" max="5" width="11.375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/src/main/resources/template/持仓列表.xlsx
+++ b/src/main/resources/template/持仓列表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\risk\src\main\resources\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2150DC8F-805F-4FF6-A278-29BA09DF762D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{546FBB77-AAA9-480C-8828-1D9D7EAB5D67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>合约</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -44,6 +44,10 @@
   </si>
   <si>
     <t>日期(yyy-MM-dd)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>币种</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -90,7 +94,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -113,13 +117,25 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -400,7 +416,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.625" customWidth="1"/>
@@ -409,7 +425,7 @@
     <col min="5" max="5" width="11.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -424,6 +440,9 @@
       </c>
       <c r="E1" s="1" t="s">
         <v>3</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/template/持仓列表.xlsx
+++ b/src/main/resources/template/持仓列表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\risk\src\main\resources\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{546FBB77-AAA9-480C-8828-1D9D7EAB5D67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{471428F9-47F9-443F-A7EA-82DAF7D30D0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>合约</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -43,11 +43,19 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>日期(yyy-MM-dd)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>币种</t>
+    <t>AAAAA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AAPL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AAPL1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>日期(yyyy-MM-dd)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -55,6 +63,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="177" formatCode="yyyy/mm/dd"/>
+  </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -94,7 +105,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -117,17 +128,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -135,7 +135,7 @@
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -416,7 +416,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.625" customWidth="1"/>
@@ -425,12 +425,12 @@
     <col min="5" max="5" width="11.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
@@ -441,8 +441,22 @@
       <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="2">
+        <v>46226</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
         <v>5</v>
+      </c>
+      <c r="E2">
+        <v>978</v>
       </c>
     </row>
   </sheetData>
